--- a/JNV_Student_Marks.xlsx
+++ b/JNV_Student_Marks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\JNV_ App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A082E7F5-DD34-4DF7-A5F2-69EA8604BAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B074B8A-801E-4CAE-91DC-17B14A36F63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="15450" xr2:uid="{38E983D3-5D8A-4B72-A05A-A26E910972CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="301">
   <si>
     <t>Roll_No</t>
   </si>
@@ -934,6 +934,12 @@
   </si>
   <si>
     <t>PWT-4</t>
+  </si>
+  <si>
+    <t>Mother_Name</t>
+  </si>
+  <si>
+    <t>Abc</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1302,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1305,7 +1311,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
@@ -1716,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542F166A-4256-4AA6-A03A-29FB16EA9D15}">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1726,7 +1732,7 @@
     <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1751,8 +1757,11 @@
       <c r="H1" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1000</v>
       </c>
@@ -1777,8 +1786,11 @@
       <c r="H2" s="48" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1001</v>
       </c>
@@ -1804,7 +1816,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1002</v>
       </c>
@@ -1830,7 +1842,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>1003</v>
       </c>
@@ -1856,7 +1868,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>1004</v>
       </c>
@@ -1882,7 +1894,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>1005</v>
       </c>
@@ -1908,7 +1920,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>1006</v>
       </c>
@@ -1934,7 +1946,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>1007</v>
       </c>
@@ -1960,7 +1972,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>1008</v>
       </c>
@@ -1986,7 +1998,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>1009</v>
       </c>
@@ -2012,7 +2024,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>1010</v>
       </c>
@@ -2038,7 +2050,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>1011</v>
       </c>
@@ -2064,7 +2076,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>1012</v>
       </c>
@@ -2090,7 +2102,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>1013</v>
       </c>
@@ -2116,7 +2128,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>1014</v>
       </c>
@@ -3927,22 +3939,22 @@
         <v>240</v>
       </c>
       <c r="E2" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F2" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G2" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H2" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I2" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J2" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K2" s="45"/>
       <c r="L2" s="45"/>
@@ -3962,22 +3974,22 @@
         <v>240</v>
       </c>
       <c r="E3" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F3" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G3" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H3" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I3" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J3" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K3" s="45"/>
       <c r="L3" s="45"/>
@@ -3997,22 +4009,22 @@
         <v>240</v>
       </c>
       <c r="E4" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F4" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G4" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H4" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I4" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J4" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K4" s="45"/>
       <c r="L4" s="45"/>
@@ -4032,22 +4044,22 @@
         <v>240</v>
       </c>
       <c r="E5" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F5" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G5" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H5" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I5" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J5" s="51">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K5" s="45"/>
       <c r="L5" s="45"/>
@@ -4067,22 +4079,22 @@
         <v>480</v>
       </c>
       <c r="E6" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F6" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G6" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H6" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I6" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J6" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K6" s="45"/>
       <c r="L6" s="45"/>
@@ -4102,22 +4114,22 @@
         <v>480</v>
       </c>
       <c r="E7" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F7" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G7" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H7" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I7" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J7" s="51">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K7" s="45"/>
       <c r="L7" s="45"/>
